--- a/results/v4主力_20260619.xlsx
+++ b/results/v4主力_20260619.xlsx
@@ -10,7 +10,8 @@
     <sheet name="A強訊號" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="B_XGB獨立" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="C_Tree獨立" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="全部" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="漲停候選" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="全部" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +506,21 @@
           <t>買超排名</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>漲停候選分數%</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>漲停模型驗證AP%</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>漲停樣本基準率%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -564,6 +580,15 @@
       <c r="Q2" t="n">
         <v>21</v>
       </c>
+      <c r="R2" t="n">
+        <v>87.30000305175781</v>
+      </c>
+      <c r="S2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -626,6 +651,15 @@
       </c>
       <c r="Q3" t="n">
         <v>9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>90.09999847412109</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -686,6 +720,15 @@
       <c r="Q4" t="n">
         <v>64</v>
       </c>
+      <c r="R4" t="n">
+        <v>91.19999694824219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -748,6 +791,15 @@
       </c>
       <c r="Q5" t="n">
         <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>91.19999694824219</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -808,6 +860,15 @@
       <c r="Q6" t="n">
         <v>58</v>
       </c>
+      <c r="R6" t="n">
+        <v>59</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -831,7 +892,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>92.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>74.7</v>
@@ -871,6 +932,15 @@
       <c r="Q7" t="n">
         <v>35</v>
       </c>
+      <c r="R7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -894,7 +964,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>90.7</v>
       </c>
       <c r="F8" t="n">
         <v>92.40000000000001</v>
@@ -934,6 +1004,15 @@
       <c r="Q8" t="n">
         <v>10</v>
       </c>
+      <c r="R8" t="n">
+        <v>77.59999847412109</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -943,17 +1022,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>91.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
@@ -970,28 +1049,37 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>65</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>68.2</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>367</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>10.63</v>
+        <v>3.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1581</v>
+        <v>11498</v>
       </c>
       <c r="Q9" t="n">
-        <v>61</v>
+        <v>43</v>
+      </c>
+      <c r="R9" t="n">
+        <v>39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -1055,6 +1143,15 @@
       </c>
       <c r="Q10" t="n">
         <v>34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>69.90000152587891</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -1115,6 +1212,15 @@
       <c r="Q11" t="n">
         <v>51</v>
       </c>
+      <c r="R11" t="n">
+        <v>86</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1124,24 +1230,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>矽科宏晟</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1155,28 +1257,37 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>82.5</v>
+        <v>61.1</v>
       </c>
       <c r="K12" t="n">
-        <v>83.3</v>
+        <v>68.2</v>
       </c>
       <c r="L12" t="n">
-        <v>700</v>
+        <v>367</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>6.14</v>
+        <v>10.63</v>
       </c>
       <c r="P12" t="n">
-        <v>5480</v>
+        <v>1581</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="R12" t="n">
+        <v>90.19999694824219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -1187,12 +1298,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1201,10 +1312,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>88.3</v>
+        <v>89.7</v>
       </c>
       <c r="F13" t="n">
-        <v>81.09999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1218,28 +1329,37 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>75.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="L13" t="n">
-        <v>459.5</v>
+        <v>700</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0149</v>
+        <v>0.0266</v>
       </c>
       <c r="N13" t="n">
-        <v>677</v>
+        <v>-0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.96</v>
+        <v>6.14</v>
       </c>
       <c r="P13" t="n">
-        <v>180890</v>
+        <v>5480</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>87.40000152587891</v>
+      </c>
+      <c r="S13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
@@ -1300,6 +1420,15 @@
       <c r="Q14" t="n">
         <v>37</v>
       </c>
+      <c r="R14" t="n">
+        <v>89.59999847412109</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1363,6 +1492,15 @@
       <c r="Q15" t="n">
         <v>15</v>
       </c>
+      <c r="R15" t="n">
+        <v>92.30000305175781</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1426,6 +1564,15 @@
       <c r="Q16" t="n">
         <v>7</v>
       </c>
+      <c r="R16" t="n">
+        <v>62.40000152587891</v>
+      </c>
+      <c r="S16" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1435,20 +1582,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>富喬</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>86.5</v>
+        <v>86.2</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>54.4</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1462,28 +1613,37 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>77.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>98.09999999999999</v>
+        <v>1080</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0315</v>
       </c>
       <c r="N17" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="O17" t="n">
-        <v>3.47</v>
+        <v>9.81</v>
       </c>
       <c r="P17" t="n">
-        <v>11498</v>
+        <v>93655</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>92.09999847412109</v>
+      </c>
+      <c r="S17" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -1494,12 +1654,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1511,7 +1671,7 @@
         <v>86.2</v>
       </c>
       <c r="F18" t="n">
-        <v>54.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1525,28 +1685,37 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L18" t="n">
-        <v>1080</v>
+        <v>459.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0315</v>
+        <v>0.0149</v>
       </c>
       <c r="N18" t="n">
-        <v>95</v>
+        <v>677</v>
       </c>
       <c r="O18" t="n">
-        <v>9.81</v>
+        <v>6.96</v>
       </c>
       <c r="P18" t="n">
-        <v>93655</v>
+        <v>180890</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="R18" t="n">
+        <v>89.40000152587891</v>
+      </c>
+      <c r="S18" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -1611,6 +1780,15 @@
       <c r="Q19" t="n">
         <v>16</v>
       </c>
+      <c r="R19" t="n">
+        <v>88.09999847412109</v>
+      </c>
+      <c r="S19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1674,6 +1852,15 @@
       <c r="Q20" t="n">
         <v>31</v>
       </c>
+      <c r="R20" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1683,17 +1870,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="F21" t="n">
         <v>100</v>
@@ -1710,28 +1897,37 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>72.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="L21" t="n">
-        <v>252</v>
+        <v>94</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0022</v>
+        <v>0.0076</v>
       </c>
       <c r="N21" t="n">
-        <v>-0</v>
+        <v>126</v>
       </c>
       <c r="O21" t="n">
-        <v>8.73</v>
+        <v>4.04</v>
       </c>
       <c r="P21" t="n">
-        <v>1933</v>
+        <v>17894</v>
       </c>
       <c r="Q21" t="n">
-        <v>63</v>
+        <v>40</v>
+      </c>
+      <c r="R21" t="n">
+        <v>61</v>
+      </c>
+      <c r="S21" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="22">
@@ -1742,20 +1938,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>艾訊</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>83.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>85.2</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1769,28 +1965,37 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>78.3</v>
+        <v>72.7</v>
       </c>
       <c r="K22" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
       <c r="L22" t="n">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>-0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.14</v>
+        <v>8.73</v>
       </c>
       <c r="P22" t="n">
-        <v>1112</v>
+        <v>1933</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>63</v>
+      </c>
+      <c r="R22" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -1801,24 +2006,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>83.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>85.2</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1832,28 +2033,37 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>88.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L23" t="n">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0458</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>5.75</v>
+        <v>4.14</v>
       </c>
       <c r="P23" t="n">
-        <v>26329</v>
+        <v>1112</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>56</v>
+      </c>
+      <c r="R23" t="n">
+        <v>26.89999961853027</v>
+      </c>
+      <c r="S23" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1864,12 +2074,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1878,10 +2088,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1895,28 +2105,37 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>77.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L24" t="n">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0988</v>
+        <v>0.0458</v>
       </c>
       <c r="N24" t="n">
-        <v>-55</v>
+        <v>50</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>5.75</v>
       </c>
       <c r="P24" t="n">
-        <v>134251</v>
+        <v>26329</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>85.80000305175781</v>
+      </c>
+      <c r="S24" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -1927,20 +2146,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>81.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1954,28 +2177,37 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>82.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="L25" t="n">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0076</v>
+        <v>0.0988</v>
       </c>
       <c r="N25" t="n">
-        <v>126</v>
+        <v>-55</v>
       </c>
       <c r="O25" t="n">
-        <v>4.04</v>
+        <v>2.88</v>
       </c>
       <c r="P25" t="n">
-        <v>17894</v>
+        <v>134251</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="R25" t="n">
+        <v>93</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -2036,6 +2268,15 @@
       <c r="Q26" t="n">
         <v>11</v>
       </c>
+      <c r="R26" t="n">
+        <v>82.90000152587891</v>
+      </c>
+      <c r="S26" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2099,6 +2340,15 @@
       <c r="Q27" t="n">
         <v>60</v>
       </c>
+      <c r="R27" t="n">
+        <v>82</v>
+      </c>
+      <c r="S27" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2122,7 +2372,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>78.7</v>
+        <v>79.3</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
@@ -2139,7 +2389,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>80.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
         <v>81.7</v>
@@ -2162,6 +2412,15 @@
       <c r="Q28" t="n">
         <v>45</v>
       </c>
+      <c r="R28" t="n">
+        <v>86.90000152587891</v>
+      </c>
+      <c r="S28" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2224,6 +2483,15 @@
       </c>
       <c r="Q29" t="n">
         <v>65</v>
+      </c>
+      <c r="R29" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="30">
@@ -2284,6 +2552,15 @@
       <c r="Q30" t="n">
         <v>39</v>
       </c>
+      <c r="R30" t="n">
+        <v>78.69999694824219</v>
+      </c>
+      <c r="S30" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2346,6 +2623,15 @@
       </c>
       <c r="Q31" t="n">
         <v>2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>89.59999847412109</v>
+      </c>
+      <c r="S31" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="32">
@@ -2406,6 +2692,15 @@
       <c r="Q32" t="n">
         <v>50</v>
       </c>
+      <c r="R32" t="n">
+        <v>85.69999694824219</v>
+      </c>
+      <c r="S32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2469,6 +2764,15 @@
       <c r="Q33" t="n">
         <v>3</v>
       </c>
+      <c r="R33" t="n">
+        <v>66.80000305175781</v>
+      </c>
+      <c r="S33" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2532,6 +2836,15 @@
       <c r="Q34" t="n">
         <v>25</v>
       </c>
+      <c r="R34" t="n">
+        <v>65</v>
+      </c>
+      <c r="S34" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2595,6 +2908,15 @@
       <c r="Q35" t="n">
         <v>22</v>
       </c>
+      <c r="R35" t="n">
+        <v>58.20000076293945</v>
+      </c>
+      <c r="S35" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2658,6 +2980,15 @@
       <c r="Q36" t="n">
         <v>12</v>
       </c>
+      <c r="R36" t="n">
+        <v>71</v>
+      </c>
+      <c r="S36" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2721,6 +3052,15 @@
       <c r="Q37" t="n">
         <v>18</v>
       </c>
+      <c r="R37" t="n">
+        <v>95.40000152587891</v>
+      </c>
+      <c r="S37" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2784,6 +3124,15 @@
       <c r="Q38" t="n">
         <v>29</v>
       </c>
+      <c r="R38" t="n">
+        <v>47.40000152587891</v>
+      </c>
+      <c r="S38" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2793,12 +3142,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>威盛</t>
+          <t>精材</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2807,10 +3156,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63.3</v>
+        <v>62.3</v>
       </c>
       <c r="F39" t="n">
-        <v>57.6</v>
+        <v>59.5</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -2824,28 +3173,37 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>78.7</v>
+        <v>74.5</v>
       </c>
       <c r="K39" t="n">
-        <v>71.7</v>
+        <v>75</v>
       </c>
       <c r="L39" t="n">
-        <v>81.40000000000001</v>
+        <v>251</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0146</v>
+        <v>-0.0041</v>
       </c>
       <c r="N39" t="n">
-        <v>-77</v>
+        <v>149</v>
       </c>
       <c r="O39" t="n">
-        <v>9.210000000000001</v>
+        <v>4.78</v>
       </c>
       <c r="P39" t="n">
-        <v>17319</v>
+        <v>3294</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="R39" t="n">
+        <v>51.59999847412109</v>
+      </c>
+      <c r="S39" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="40">
@@ -2856,12 +3214,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>精材</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2870,10 +3228,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>62.3</v>
+        <v>61.3</v>
       </c>
       <c r="F40" t="n">
-        <v>59.5</v>
+        <v>85</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -2887,28 +3245,37 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>74.5</v>
+        <v>54.5</v>
       </c>
       <c r="K40" t="n">
-        <v>75</v>
+        <v>36.7</v>
       </c>
       <c r="L40" t="n">
-        <v>251</v>
+        <v>42.55</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0041</v>
+        <v>0.0176</v>
       </c>
       <c r="N40" t="n">
-        <v>149</v>
+        <v>747</v>
       </c>
       <c r="O40" t="n">
-        <v>4.78</v>
+        <v>3.41</v>
       </c>
       <c r="P40" t="n">
-        <v>3294</v>
+        <v>-38390</v>
       </c>
       <c r="Q40" t="n">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="R40" t="n">
+        <v>49.79999923706055</v>
+      </c>
+      <c r="S40" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="41">
@@ -2919,12 +3286,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>威盛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2933,10 +3300,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>61.3</v>
+        <v>60.3</v>
       </c>
       <c r="F41" t="n">
-        <v>85</v>
+        <v>57.6</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -2950,28 +3317,37 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>54.5</v>
+        <v>78.7</v>
       </c>
       <c r="K41" t="n">
-        <v>36.7</v>
+        <v>71.7</v>
       </c>
       <c r="L41" t="n">
-        <v>42.55</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0176</v>
+        <v>0.0146</v>
       </c>
       <c r="N41" t="n">
-        <v>747</v>
+        <v>-77</v>
       </c>
       <c r="O41" t="n">
-        <v>3.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>-38390</v>
+        <v>17319</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="R41" t="n">
+        <v>84.69999694824219</v>
+      </c>
+      <c r="S41" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="42">
@@ -3036,6 +3412,15 @@
       <c r="Q42" t="n">
         <v>4</v>
       </c>
+      <c r="R42" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="S42" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3099,6 +3484,15 @@
       <c r="Q43" t="n">
         <v>24</v>
       </c>
+      <c r="R43" t="n">
+        <v>10.19999980926514</v>
+      </c>
+      <c r="S43" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3161,6 +3555,15 @@
       </c>
       <c r="Q44" t="n">
         <v>36</v>
+      </c>
+      <c r="R44" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3174,7 +3577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3263,6 +3666,21 @@
           <t>買超排名</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>漲停候選分數%</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>漲停模型驗證AP%</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>漲停樣本基準率%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3325,6 +3743,15 @@
       </c>
       <c r="Q2" t="n">
         <v>26</v>
+      </c>
+      <c r="R2" t="n">
+        <v>16.89999961853027</v>
+      </c>
+      <c r="S2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -3385,6 +3812,15 @@
       <c r="Q3" t="n">
         <v>46</v>
       </c>
+      <c r="R3" t="n">
+        <v>68.90000152587891</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3444,6 +3880,15 @@
       <c r="Q4" t="n">
         <v>62</v>
       </c>
+      <c r="R4" t="n">
+        <v>66</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3506,6 +3951,15 @@
       </c>
       <c r="Q5" t="n">
         <v>59</v>
+      </c>
+      <c r="R5" t="n">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -3566,6 +4020,15 @@
       <c r="Q6" t="n">
         <v>57</v>
       </c>
+      <c r="R6" t="n">
+        <v>59.40000152587891</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3625,6 +4088,15 @@
       <c r="Q7" t="n">
         <v>41</v>
       </c>
+      <c r="R7" t="n">
+        <v>92.59999847412109</v>
+      </c>
+      <c r="S7" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3687,6 +4159,15 @@
       </c>
       <c r="Q8" t="n">
         <v>13</v>
+      </c>
+      <c r="R8" t="n">
+        <v>45.79999923706055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -3747,6 +4228,15 @@
       <c r="Q9" t="n">
         <v>54</v>
       </c>
+      <c r="R9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3806,6 +4296,15 @@
       <c r="Q10" t="n">
         <v>48</v>
       </c>
+      <c r="R10" t="n">
+        <v>77.19999694824219</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3868,6 +4367,15 @@
       </c>
       <c r="Q11" t="n">
         <v>27</v>
+      </c>
+      <c r="R11" t="n">
+        <v>87.69999694824219</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3881,7 +4389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3970,6 +4478,21 @@
           <t>買超排名</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>漲停候選分數%</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>漲停模型驗證AP%</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>漲停樣本基準率%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4033,6 +4556,15 @@
       <c r="Q2" t="n">
         <v>53</v>
       </c>
+      <c r="R2" t="n">
+        <v>31.89999961853027</v>
+      </c>
+      <c r="S2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4096,6 +4628,15 @@
       <c r="Q3" t="n">
         <v>28</v>
       </c>
+      <c r="R3" t="n">
+        <v>19.60000038146973</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4158,6 +4699,15 @@
       </c>
       <c r="Q4" t="n">
         <v>32</v>
+      </c>
+      <c r="R4" t="n">
+        <v>95.90000152587891</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -4171,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4260,6 +4810,1545 @@
           <t>買超排名</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>漲停候選分數%</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>漲停模型驗證AP%</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>漲停樣本基準率%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C Tree獨立</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L2" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>32</v>
+      </c>
+      <c r="R2" t="n">
+        <v>95.90000152587891</v>
+      </c>
+      <c r="S2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L3" t="n">
+        <v>160</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-269</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R3" t="n">
+        <v>95.40000152587891</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="K4" t="n">
+        <v>80</v>
+      </c>
+      <c r="L4" t="n">
+        <v>139</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P4" t="n">
+        <v>134251</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>19</v>
+      </c>
+      <c r="R4" t="n">
+        <v>93</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B XGB獨立</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>光頡</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>41</v>
+      </c>
+      <c r="R5" t="n">
+        <v>92.59999847412109</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>華紙</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="N6" t="n">
+        <v>264</v>
+      </c>
+      <c r="O6" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="P6" t="n">
+        <v>44191</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15</v>
+      </c>
+      <c r="R6" t="n">
+        <v>92.30000305175781</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1080</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="N7" t="n">
+        <v>95</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="P7" t="n">
+        <v>93655</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>14</v>
+      </c>
+      <c r="R7" t="n">
+        <v>92.09999847412109</v>
+      </c>
+      <c r="S7" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>145</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8650</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>42</v>
+      </c>
+      <c r="R8" t="n">
+        <v>91.30000305175781</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>群創</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>76</v>
+      </c>
+      <c r="K9" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3136</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>860943</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>91.19999694824219</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>百徽</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3646</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>64</v>
+      </c>
+      <c r="R10" t="n">
+        <v>91.19999694824219</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D 無訊號</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8255</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>朋程</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>195</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0789</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2827</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>47</v>
+      </c>
+      <c r="R11" t="n">
+        <v>90.90000152587891</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6725</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>矽科宏晟</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>367</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1581</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>61</v>
+      </c>
+      <c r="R12" t="n">
+        <v>90.19999694824219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>南茂</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>104</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="N13" t="n">
+        <v>23</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="P13" t="n">
+        <v>73244</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>90.09999847412109</v>
+      </c>
+      <c r="S13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2796</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="P14" t="n">
+        <v>337984</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>89.59999847412109</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>華容</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>43096</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>37</v>
+      </c>
+      <c r="R15" t="n">
+        <v>89.59999847412109</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>459.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="N16" t="n">
+        <v>677</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="P16" t="n">
+        <v>180890</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>23</v>
+      </c>
+      <c r="R16" t="n">
+        <v>89.40000152587891</v>
+      </c>
+      <c r="S16" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5475</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>德宏</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>84</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>252</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1933</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>63</v>
+      </c>
+      <c r="R17" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80</v>
+      </c>
+      <c r="L18" t="n">
+        <v>235</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="P18" t="n">
+        <v>17090</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>16</v>
+      </c>
+      <c r="R18" t="n">
+        <v>88.09999847412109</v>
+      </c>
+      <c r="S18" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B XGB獨立</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2332</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>友訊</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>60</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-120</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P19" t="n">
+        <v>16827</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>27</v>
+      </c>
+      <c r="R19" t="n">
+        <v>87.69999694824219</v>
+      </c>
+      <c r="S19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>金居</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>700</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5480</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>44</v>
+      </c>
+      <c r="R20" t="n">
+        <v>87.40000152587891</v>
+      </c>
+      <c r="S20" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 強訊號</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>東鹼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-336</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P21" t="n">
+        <v>21182</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>21</v>
+      </c>
+      <c r="R21" t="n">
+        <v>87.30000305175781</v>
+      </c>
+      <c r="S21" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股名</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>有期貨</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>XGB信心%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tree信心%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>xgboost</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>s_Tree</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>模型資料日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>XGB驗證精準率%</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>驗證基準命中率%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>預測日收盤</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>開收比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>實際差異數</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>價差對比</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>控一</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>買超排名</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>漲停候選分數%</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>漲停模型驗證AP%</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>漲停樣本基準率%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4319,6 +6408,15 @@
       <c r="Q2" t="n">
         <v>21</v>
       </c>
+      <c r="R2" t="n">
+        <v>87.30000305175781</v>
+      </c>
+      <c r="S2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4381,6 +6479,15 @@
       </c>
       <c r="Q3" t="n">
         <v>9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>90.09999847412109</v>
+      </c>
+      <c r="S3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -4441,6 +6548,15 @@
       <c r="Q4" t="n">
         <v>64</v>
       </c>
+      <c r="R4" t="n">
+        <v>91.19999694824219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4503,6 +6619,15 @@
       </c>
       <c r="Q5" t="n">
         <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>91.19999694824219</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -4563,6 +6688,15 @@
       <c r="Q6" t="n">
         <v>58</v>
       </c>
+      <c r="R6" t="n">
+        <v>59</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4586,7 +6720,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>92.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>74.7</v>
@@ -4626,6 +6760,15 @@
       <c r="Q7" t="n">
         <v>35</v>
       </c>
+      <c r="R7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4649,7 +6792,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>90.7</v>
       </c>
       <c r="F8" t="n">
         <v>92.40000000000001</v>
@@ -4689,6 +6832,15 @@
       <c r="Q8" t="n">
         <v>10</v>
       </c>
+      <c r="R8" t="n">
+        <v>77.59999847412109</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4698,17 +6850,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>91.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F9" t="n">
         <v>100</v>
@@ -4725,28 +6877,37 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>65</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>68.2</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>367</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>10.63</v>
+        <v>3.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1581</v>
+        <v>11498</v>
       </c>
       <c r="Q9" t="n">
-        <v>61</v>
+        <v>43</v>
+      </c>
+      <c r="R9" t="n">
+        <v>39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -4810,6 +6971,15 @@
       </c>
       <c r="Q10" t="n">
         <v>34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>69.90000152587891</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -4870,6 +7040,15 @@
       <c r="Q11" t="n">
         <v>51</v>
       </c>
+      <c r="R11" t="n">
+        <v>86</v>
+      </c>
+      <c r="S11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4879,24 +7058,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>金居</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>矽科宏晟</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>89.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -4910,28 +7085,37 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>82.5</v>
+        <v>61.1</v>
       </c>
       <c r="K12" t="n">
-        <v>83.3</v>
+        <v>68.2</v>
       </c>
       <c r="L12" t="n">
-        <v>700</v>
+        <v>367</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>6.14</v>
+        <v>10.63</v>
       </c>
       <c r="P12" t="n">
-        <v>5480</v>
+        <v>1581</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="R12" t="n">
+        <v>90.19999694824219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -4942,12 +7126,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4956,10 +7140,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>88.3</v>
+        <v>89.7</v>
       </c>
       <c r="F13" t="n">
-        <v>81.09999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -4973,28 +7157,37 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>75.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="L13" t="n">
-        <v>459.5</v>
+        <v>700</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0149</v>
+        <v>0.0266</v>
       </c>
       <c r="N13" t="n">
-        <v>677</v>
+        <v>-0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.96</v>
+        <v>6.14</v>
       </c>
       <c r="P13" t="n">
-        <v>180890</v>
+        <v>5480</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="R13" t="n">
+        <v>87.40000152587891</v>
+      </c>
+      <c r="S13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
@@ -5055,6 +7248,15 @@
       <c r="Q14" t="n">
         <v>37</v>
       </c>
+      <c r="R14" t="n">
+        <v>89.59999847412109</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5118,6 +7320,15 @@
       <c r="Q15" t="n">
         <v>15</v>
       </c>
+      <c r="R15" t="n">
+        <v>92.30000305175781</v>
+      </c>
+      <c r="S15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5181,6 +7392,15 @@
       <c r="Q16" t="n">
         <v>7</v>
       </c>
+      <c r="R16" t="n">
+        <v>62.40000152587891</v>
+      </c>
+      <c r="S16" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5190,20 +7410,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>富喬</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E17" t="n">
-        <v>86.5</v>
+        <v>86.2</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>54.4</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -5217,28 +7441,37 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>77.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>98.09999999999999</v>
+        <v>1080</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0315</v>
       </c>
       <c r="N17" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="O17" t="n">
-        <v>3.47</v>
+        <v>9.81</v>
       </c>
       <c r="P17" t="n">
-        <v>11498</v>
+        <v>93655</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="R17" t="n">
+        <v>92.09999847412109</v>
+      </c>
+      <c r="S17" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -5249,12 +7482,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5266,7 +7499,7 @@
         <v>86.2</v>
       </c>
       <c r="F18" t="n">
-        <v>54.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -5280,28 +7513,37 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L18" t="n">
-        <v>1080</v>
+        <v>459.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0315</v>
+        <v>0.0149</v>
       </c>
       <c r="N18" t="n">
-        <v>95</v>
+        <v>677</v>
       </c>
       <c r="O18" t="n">
-        <v>9.81</v>
+        <v>6.96</v>
       </c>
       <c r="P18" t="n">
-        <v>93655</v>
+        <v>180890</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="R18" t="n">
+        <v>89.40000152587891</v>
+      </c>
+      <c r="S18" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -5366,6 +7608,15 @@
       <c r="Q19" t="n">
         <v>16</v>
       </c>
+      <c r="R19" t="n">
+        <v>88.09999847412109</v>
+      </c>
+      <c r="S19" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5429,6 +7680,15 @@
       <c r="Q20" t="n">
         <v>31</v>
       </c>
+      <c r="R20" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5438,17 +7698,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>德宏</t>
+          <t>鈺創</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="F21" t="n">
         <v>100</v>
@@ -5465,28 +7725,37 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>72.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="L21" t="n">
-        <v>252</v>
+        <v>94</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0022</v>
+        <v>0.0076</v>
       </c>
       <c r="N21" t="n">
-        <v>-0</v>
+        <v>126</v>
       </c>
       <c r="O21" t="n">
-        <v>8.73</v>
+        <v>4.04</v>
       </c>
       <c r="P21" t="n">
-        <v>1933</v>
+        <v>17894</v>
       </c>
       <c r="Q21" t="n">
-        <v>63</v>
+        <v>40</v>
+      </c>
+      <c r="R21" t="n">
+        <v>61</v>
+      </c>
+      <c r="S21" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="22">
@@ -5497,20 +7766,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>艾訊</t>
+          <t>德宏</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>83.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>85.2</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -5524,28 +7793,37 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>78.3</v>
+        <v>72.7</v>
       </c>
       <c r="K22" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
       <c r="L22" t="n">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>-0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.14</v>
+        <v>8.73</v>
       </c>
       <c r="P22" t="n">
-        <v>1112</v>
+        <v>1933</v>
       </c>
       <c r="Q22" t="n">
-        <v>56</v>
+        <v>63</v>
+      </c>
+      <c r="R22" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="S22" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -5556,24 +7834,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>頎邦</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>83.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>85.2</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -5587,28 +7861,37 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>88.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="L23" t="n">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0458</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>5.75</v>
+        <v>4.14</v>
       </c>
       <c r="P23" t="n">
-        <v>26329</v>
+        <v>1112</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>56</v>
+      </c>
+      <c r="R23" t="n">
+        <v>26.89999961853027</v>
+      </c>
+      <c r="S23" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -5619,12 +7902,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5633,10 +7916,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>82.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -5650,28 +7933,37 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>77.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L24" t="n">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0988</v>
+        <v>0.0458</v>
       </c>
       <c r="N24" t="n">
-        <v>-55</v>
+        <v>50</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>5.75</v>
       </c>
       <c r="P24" t="n">
-        <v>134251</v>
+        <v>26329</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>85.80000305175781</v>
+      </c>
+      <c r="S24" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -5682,20 +7974,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>鈺創</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E25" t="n">
-        <v>81.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -5709,28 +8005,37 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>82.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>83.3</v>
+        <v>80</v>
       </c>
       <c r="L25" t="n">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0076</v>
+        <v>0.0988</v>
       </c>
       <c r="N25" t="n">
-        <v>126</v>
+        <v>-55</v>
       </c>
       <c r="O25" t="n">
-        <v>4.04</v>
+        <v>2.88</v>
       </c>
       <c r="P25" t="n">
-        <v>17894</v>
+        <v>134251</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="R25" t="n">
+        <v>93</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -5791,6 +8096,15 @@
       <c r="Q26" t="n">
         <v>11</v>
       </c>
+      <c r="R26" t="n">
+        <v>82.90000152587891</v>
+      </c>
+      <c r="S26" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5854,6 +8168,15 @@
       <c r="Q27" t="n">
         <v>60</v>
       </c>
+      <c r="R27" t="n">
+        <v>82</v>
+      </c>
+      <c r="S27" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5877,7 +8200,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>78.7</v>
+        <v>79.3</v>
       </c>
       <c r="F28" t="n">
         <v>100</v>
@@ -5894,7 +8217,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>80.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
         <v>81.7</v>
@@ -5917,6 +8240,15 @@
       <c r="Q28" t="n">
         <v>45</v>
       </c>
+      <c r="R28" t="n">
+        <v>86.90000152587891</v>
+      </c>
+      <c r="S28" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5979,6 +8311,15 @@
       </c>
       <c r="Q29" t="n">
         <v>65</v>
+      </c>
+      <c r="R29" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="30">
@@ -6039,6 +8380,15 @@
       <c r="Q30" t="n">
         <v>39</v>
       </c>
+      <c r="R30" t="n">
+        <v>78.69999694824219</v>
+      </c>
+      <c r="S30" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6101,6 +8451,15 @@
       </c>
       <c r="Q31" t="n">
         <v>2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>89.59999847412109</v>
+      </c>
+      <c r="S31" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="32">
@@ -6161,6 +8520,15 @@
       <c r="Q32" t="n">
         <v>50</v>
       </c>
+      <c r="R32" t="n">
+        <v>85.69999694824219</v>
+      </c>
+      <c r="S32" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6224,6 +8592,15 @@
       <c r="Q33" t="n">
         <v>3</v>
       </c>
+      <c r="R33" t="n">
+        <v>66.80000305175781</v>
+      </c>
+      <c r="S33" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6287,6 +8664,15 @@
       <c r="Q34" t="n">
         <v>25</v>
       </c>
+      <c r="R34" t="n">
+        <v>65</v>
+      </c>
+      <c r="S34" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6350,6 +8736,15 @@
       <c r="Q35" t="n">
         <v>22</v>
       </c>
+      <c r="R35" t="n">
+        <v>58.20000076293945</v>
+      </c>
+      <c r="S35" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6413,6 +8808,15 @@
       <c r="Q36" t="n">
         <v>12</v>
       </c>
+      <c r="R36" t="n">
+        <v>71</v>
+      </c>
+      <c r="S36" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6476,6 +8880,15 @@
       <c r="Q37" t="n">
         <v>18</v>
       </c>
+      <c r="R37" t="n">
+        <v>95.40000152587891</v>
+      </c>
+      <c r="S37" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6539,6 +8952,15 @@
       <c r="Q38" t="n">
         <v>29</v>
       </c>
+      <c r="R38" t="n">
+        <v>47.40000152587891</v>
+      </c>
+      <c r="S38" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6548,12 +8970,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>威盛</t>
+          <t>精材</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6562,10 +8984,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>63.3</v>
+        <v>62.3</v>
       </c>
       <c r="F39" t="n">
-        <v>57.6</v>
+        <v>59.5</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -6579,28 +9001,37 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>78.7</v>
+        <v>74.5</v>
       </c>
       <c r="K39" t="n">
-        <v>71.7</v>
+        <v>75</v>
       </c>
       <c r="L39" t="n">
-        <v>81.40000000000001</v>
+        <v>251</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0146</v>
+        <v>-0.0041</v>
       </c>
       <c r="N39" t="n">
-        <v>-77</v>
+        <v>149</v>
       </c>
       <c r="O39" t="n">
-        <v>9.210000000000001</v>
+        <v>4.78</v>
       </c>
       <c r="P39" t="n">
-        <v>17319</v>
+        <v>3294</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="R39" t="n">
+        <v>51.59999847412109</v>
+      </c>
+      <c r="S39" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="40">
@@ -6611,12 +9042,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>精材</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6625,10 +9056,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>62.3</v>
+        <v>61.3</v>
       </c>
       <c r="F40" t="n">
-        <v>59.5</v>
+        <v>85</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -6642,28 +9073,37 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>74.5</v>
+        <v>54.5</v>
       </c>
       <c r="K40" t="n">
-        <v>75</v>
+        <v>36.7</v>
       </c>
       <c r="L40" t="n">
-        <v>251</v>
+        <v>42.55</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0041</v>
+        <v>0.0176</v>
       </c>
       <c r="N40" t="n">
-        <v>149</v>
+        <v>747</v>
       </c>
       <c r="O40" t="n">
-        <v>4.78</v>
+        <v>3.41</v>
       </c>
       <c r="P40" t="n">
-        <v>3294</v>
+        <v>-38390</v>
       </c>
       <c r="Q40" t="n">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="R40" t="n">
+        <v>49.79999923706055</v>
+      </c>
+      <c r="S40" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="41">
@@ -6674,12 +9114,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>威盛</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6688,10 +9128,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>61.3</v>
+        <v>60.3</v>
       </c>
       <c r="F41" t="n">
-        <v>85</v>
+        <v>57.6</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -6705,28 +9145,37 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>54.5</v>
+        <v>78.7</v>
       </c>
       <c r="K41" t="n">
-        <v>36.7</v>
+        <v>71.7</v>
       </c>
       <c r="L41" t="n">
-        <v>42.55</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0176</v>
+        <v>0.0146</v>
       </c>
       <c r="N41" t="n">
-        <v>747</v>
+        <v>-77</v>
       </c>
       <c r="O41" t="n">
-        <v>3.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>-38390</v>
+        <v>17319</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="R41" t="n">
+        <v>84.69999694824219</v>
+      </c>
+      <c r="S41" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="42">
@@ -6791,6 +9240,15 @@
       <c r="Q42" t="n">
         <v>4</v>
       </c>
+      <c r="R42" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="S42" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6854,6 +9312,15 @@
       <c r="Q43" t="n">
         <v>24</v>
       </c>
+      <c r="R43" t="n">
+        <v>10.19999980926514</v>
+      </c>
+      <c r="S43" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6917,6 +9384,15 @@
       <c r="Q44" t="n">
         <v>36</v>
       </c>
+      <c r="R44" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6979,6 +9455,15 @@
       </c>
       <c r="Q45" t="n">
         <v>26</v>
+      </c>
+      <c r="R45" t="n">
+        <v>16.89999961853027</v>
+      </c>
+      <c r="S45" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="46">
@@ -7039,6 +9524,15 @@
       <c r="Q46" t="n">
         <v>46</v>
       </c>
+      <c r="R46" t="n">
+        <v>68.90000152587891</v>
+      </c>
+      <c r="S46" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7098,6 +9592,15 @@
       <c r="Q47" t="n">
         <v>62</v>
       </c>
+      <c r="R47" t="n">
+        <v>66</v>
+      </c>
+      <c r="S47" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7160,6 +9663,15 @@
       </c>
       <c r="Q48" t="n">
         <v>59</v>
+      </c>
+      <c r="R48" t="n">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="S48" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="49">
@@ -7220,6 +9732,15 @@
       <c r="Q49" t="n">
         <v>57</v>
       </c>
+      <c r="R49" t="n">
+        <v>59.40000152587891</v>
+      </c>
+      <c r="S49" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7279,6 +9800,15 @@
       <c r="Q50" t="n">
         <v>41</v>
       </c>
+      <c r="R50" t="n">
+        <v>92.59999847412109</v>
+      </c>
+      <c r="S50" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7341,6 +9871,15 @@
       </c>
       <c r="Q51" t="n">
         <v>13</v>
+      </c>
+      <c r="R51" t="n">
+        <v>45.79999923706055</v>
+      </c>
+      <c r="S51" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="52">
@@ -7401,6 +9940,15 @@
       <c r="Q52" t="n">
         <v>54</v>
       </c>
+      <c r="R52" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S52" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7460,6 +10008,15 @@
       <c r="Q53" t="n">
         <v>48</v>
       </c>
+      <c r="R53" t="n">
+        <v>77.19999694824219</v>
+      </c>
+      <c r="S53" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7523,6 +10080,15 @@
       <c r="Q54" t="n">
         <v>27</v>
       </c>
+      <c r="R54" t="n">
+        <v>87.69999694824219</v>
+      </c>
+      <c r="S54" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7586,6 +10152,15 @@
       <c r="Q55" t="n">
         <v>53</v>
       </c>
+      <c r="R55" t="n">
+        <v>31.89999961853027</v>
+      </c>
+      <c r="S55" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7649,6 +10224,15 @@
       <c r="Q56" t="n">
         <v>28</v>
       </c>
+      <c r="R56" t="n">
+        <v>19.60000038146973</v>
+      </c>
+      <c r="S56" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7712,6 +10296,15 @@
       <c r="Q57" t="n">
         <v>32</v>
       </c>
+      <c r="R57" t="n">
+        <v>95.90000152587891</v>
+      </c>
+      <c r="S57" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7735,7 +10328,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
       <c r="F58" t="n">
         <v>15.7</v>
@@ -7752,7 +10345,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>82</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K58" t="n">
         <v>78.3</v>
@@ -7774,6 +10367,15 @@
       </c>
       <c r="Q58" t="n">
         <v>49</v>
+      </c>
+      <c r="R58" t="n">
+        <v>73.09999847412109</v>
+      </c>
+      <c r="S58" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="59">
@@ -7834,6 +10436,15 @@
       <c r="Q59" t="n">
         <v>47</v>
       </c>
+      <c r="R59" t="n">
+        <v>90.90000152587891</v>
+      </c>
+      <c r="S59" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7843,12 +10454,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7857,10 +10468,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="F60" t="n">
-        <v>45.1</v>
+        <v>25.8</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -7874,28 +10485,37 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>76.5</v>
+        <v>27</v>
       </c>
       <c r="K60" t="n">
-        <v>78.3</v>
+        <v>26.7</v>
       </c>
       <c r="L60" t="n">
-        <v>2530</v>
+        <v>19.1</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0086</v>
+        <v>0.0027</v>
       </c>
       <c r="N60" t="n">
-        <v>134</v>
+        <v>-1987</v>
       </c>
       <c r="O60" t="n">
-        <v>7.91</v>
+        <v>1.83</v>
       </c>
       <c r="P60" t="n">
-        <v>7775</v>
+        <v>386563</v>
       </c>
       <c r="Q60" t="n">
-        <v>55</v>
+        <v>5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="61">
@@ -7906,24 +10526,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>中鋼</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
+          <t>光環</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>44.8</v>
+        <v>44</v>
       </c>
       <c r="F61" t="n">
-        <v>25.8</v>
+        <v>45.9</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -7937,28 +10553,37 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>27</v>
+        <v>66.7</v>
       </c>
       <c r="K61" t="n">
-        <v>26.7</v>
+        <v>66.7</v>
       </c>
       <c r="L61" t="n">
-        <v>19.1</v>
+        <v>145</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0027</v>
+        <v>0.0076</v>
       </c>
       <c r="N61" t="n">
-        <v>-1987</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1.83</v>
+        <v>10.69</v>
       </c>
       <c r="P61" t="n">
-        <v>386563</v>
+        <v>8650</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="R61" t="n">
+        <v>91.30000305175781</v>
+      </c>
+      <c r="S61" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="62">
@@ -7969,20 +10594,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>光環</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
       <c r="E62" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="F62" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -7996,28 +10625,37 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>66.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>66.7</v>
+        <v>68.3</v>
       </c>
       <c r="L62" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0076</v>
+        <v>0.0155</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>-707</v>
       </c>
       <c r="O62" t="n">
-        <v>10.69</v>
+        <v>5.33</v>
       </c>
       <c r="P62" t="n">
-        <v>8650</v>
+        <v>56145</v>
       </c>
       <c r="Q62" t="n">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="R62" t="n">
+        <v>71.69999694824219</v>
+      </c>
+      <c r="S62" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="63">
@@ -8028,12 +10666,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8042,10 +10680,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
       <c r="F63" t="n">
-        <v>46.9</v>
+        <v>36.4</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -8059,28 +10697,37 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>70.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K63" t="n">
-        <v>68.3</v>
+        <v>16.7</v>
       </c>
       <c r="L63" t="n">
-        <v>169</v>
+        <v>24.75</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0155</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>-707</v>
+        <v>256</v>
       </c>
       <c r="O63" t="n">
-        <v>5.33</v>
+        <v>1.21</v>
       </c>
       <c r="P63" t="n">
-        <v>56145</v>
+        <v>-22043</v>
       </c>
       <c r="Q63" t="n">
+        <v>30</v>
+      </c>
+      <c r="R63" t="n">
         <v>6</v>
+      </c>
+      <c r="S63" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="64">
@@ -8091,12 +10738,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8105,10 +10752,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>43.1</v>
+        <v>38.3</v>
       </c>
       <c r="F64" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -8122,28 +10769,37 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="K64" t="n">
-        <v>16.7</v>
+        <v>35</v>
       </c>
       <c r="L64" t="n">
-        <v>24.75</v>
+        <v>39.8</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>0.0344</v>
       </c>
       <c r="N64" t="n">
-        <v>256</v>
+        <v>-787</v>
       </c>
       <c r="O64" t="n">
-        <v>1.21</v>
+        <v>6.78</v>
       </c>
       <c r="P64" t="n">
-        <v>-22043</v>
+        <v>137000</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="R64" t="n">
+        <v>83.69999694824219</v>
+      </c>
+      <c r="S64" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="65">
@@ -8154,12 +10810,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8168,10 +10824,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>38.3</v>
+        <v>33.6</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>45.1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -8185,28 +10841,37 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>33.3</v>
+        <v>79.2</v>
       </c>
       <c r="K65" t="n">
-        <v>35</v>
+        <v>78.3</v>
       </c>
       <c r="L65" t="n">
-        <v>39.8</v>
+        <v>2530</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0344</v>
+        <v>0.0086</v>
       </c>
       <c r="N65" t="n">
-        <v>-787</v>
+        <v>134</v>
       </c>
       <c r="O65" t="n">
-        <v>6.78</v>
+        <v>7.91</v>
       </c>
       <c r="P65" t="n">
-        <v>137000</v>
+        <v>7775</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>55</v>
+      </c>
+      <c r="R65" t="n">
+        <v>78.69999694824219</v>
+      </c>
+      <c r="S65" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="66">
@@ -8266,6 +10931,15 @@
       </c>
       <c r="Q66" t="n">
         <v>38</v>
+      </c>
+      <c r="R66" t="n">
+        <v>85.40000152587891</v>
+      </c>
+      <c r="S66" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
